--- a/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
+++ b/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25165\AppData\Local\Kingsoft\WPS Office\12.1.0.28505\office6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25165\AppData\Local\Kingsoft\WPS Office\12.1.0.29161\office6\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
   <si>
     <t>任务编号</t>
   </si>
@@ -157,19 +157,73 @@
     <t>T2.1</t>
   </si>
   <si>
-    <t>T2.1 需求调研与竞品分析</t>
+    <t>T2.1 调研方案与问卷设计</t>
+  </si>
+  <si>
+    <t>调研方案、问卷与访谈提纲</t>
+  </si>
+  <si>
+    <t>T2.2</t>
+  </si>
+  <si>
+    <t>T2.2 问卷发放与回收（≥200 份）</t>
   </si>
   <si>
     <t>W5</t>
   </si>
   <si>
-    <t>调研记录、竞品分析表</t>
-  </si>
-  <si>
-    <t>T2.2</t>
-  </si>
-  <si>
-    <t>T2.2 可行性分析报告</t>
+    <t>问卷原始数据</t>
+  </si>
+  <si>
+    <t>T2.3</t>
+  </si>
+  <si>
+    <t>T2.3 竞品分析与群内供需观察</t>
+  </si>
+  <si>
+    <t>竞品对比表、群内观察记录</t>
+  </si>
+  <si>
+    <t>T2.4</t>
+  </si>
+  <si>
+    <t>T2.4 调研数据整理与统计</t>
+  </si>
+  <si>
+    <t>调研数据小结</t>
+  </si>
+  <si>
+    <t>T2.5</t>
+  </si>
+  <si>
+    <t>T2.5 技术可行性验证（云开发原型）</t>
+  </si>
+  <si>
+    <t>技术验证结论与原型截图</t>
+  </si>
+  <si>
+    <t>T2.6</t>
+  </si>
+  <si>
+    <t>T2.6 成本与效益测算</t>
+  </si>
+  <si>
+    <t>成本测算表、收益/投资比测算</t>
+  </si>
+  <si>
+    <t>T2.7</t>
+  </si>
+  <si>
+    <t>T2.7 合规与主体资质核查</t>
+  </si>
+  <si>
+    <t>合规核查记录、资质路径结论</t>
+  </si>
+  <si>
+    <t>T2.8</t>
+  </si>
+  <si>
+    <t>T2.8 可行性分析报告撰写（GB 8567）</t>
   </si>
   <si>
     <t>可行性分析报告（10/21）</t>
@@ -1473,9 +1527,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>任务计划!$B$2:$B$39</c:f>
+              <c:f>任务计划!$B$2:$B$45</c:f>
               <c:strCache>
-                <c:ptCount val="38"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>T1.1 选题、分组与预备作业</c:v>
                 </c:pt>
@@ -1498,96 +1552,114 @@
                   <c:v>T1.7 项目计划汇报 PPT 制作与宣讲</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>T2.1 需求调研与竞品分析</c:v>
+                  <c:v>T2.1 调研方案与问卷设计</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>T2.2 可行性分析报告</c:v>
+                  <c:v>T2.2 问卷发放与回收（≥200 份）</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>T2.3 竞品分析与群内供需观察</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>T2.4 调研数据整理与统计</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>T2.5 技术可行性验证（云开发原型）</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>T2.6 成本与效益测算</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>T2.7 合规与主体资质核查</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>T2.8 可行性分析报告撰写（GB 8567）</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>T3.1 需求获取与建模（用例/数据流）</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="16">
                   <c:v>T3.2 需求规格说明书 SRS</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="17">
                   <c:v>T3.3 需求评审 PPT 与答辩</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="18">
                   <c:v>T3.4 SRS 修订</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="19">
                   <c:v>T4.1 总体设计报告</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="20">
                   <c:v>T4.2 交互原型与 UI 视觉设计</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="21">
                   <c:v>T4.3 数据库与接口设计</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="22">
                   <c:v>T5.1 详细设计报告</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="23">
                   <c:v>T5.2 设计评审 PPT（翻转 PPT1）</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="24">
                   <c:v>T5.3 设计修订与接口冻结</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="25">
                   <c:v>T6.1 框架搭建与登录认证</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="26">
                   <c:v>T6.2 快递代取模块开发</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="27">
                   <c:v>T6.3 二手教材模块开发</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="28">
                   <c:v>T6.4 云函数与数据库实现</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="29">
                   <c:v>T6.5 积分账本与风控规则</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="30">
                   <c:v>T6.6 信用评价与申诉模块</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="31">
                   <c:v>T6.7 地图与消息推送对接</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="32">
                   <c:v>T6.8 集成联调与代码清单（翻转PPT2）</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="33">
                   <c:v>T7.1 测试用例设计</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="34">
                   <c:v>T7.2 功能与边界测试</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="35">
                   <c:v>T7.3 并发与积分一致性测试</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="36">
                   <c:v>T7.4 系统测试报告</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="37">
                   <c:v>T7.5 测试评审与缺陷修复</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="38">
                   <c:v>T8.1 性能与体验优化</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="39">
                   <c:v>T8.2 单校区试运行与用户反馈</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="40">
                   <c:v>T8.3 用户使用手册编写</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="41">
                   <c:v>T9.1 项目总结报告</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="42">
                   <c:v>T9.2 总评审 PPT 与答辩</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="43">
                   <c:v>T9.3 课程作业评审与资料归档</c:v>
                 </c:pt>
               </c:strCache>
@@ -1595,10 +1667,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>任务计划!$D$2:$D$39</c:f>
+              <c:f>任务计划!$D$2:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1627,43 +1699,43 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="16">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="17">
                   <c:v>5</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="18">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="19">
                   <c:v>7</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="20">
                   <c:v>6</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="21">
                   <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>8</c:v>
@@ -1675,42 +1747,60 @@
                   <c:v>9</c:v>
                 </c:pt>
                 <c:pt idx="25">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="32">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="33">
                   <c:v>10</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="34">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="35">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="36">
                   <c:v>11</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="37">
                   <c:v>12</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="38">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="39">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="40">
                   <c:v>13</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="41">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="42">
                   <c:v>14</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="43">
                   <c:v>15</c:v>
                 </c:pt>
               </c:numCache>
@@ -1793,6 +1883,19 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
+            <c:idx val="8"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0EA5E9"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
             <c:idx val="9"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
@@ -1806,20 +1909,7 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="11"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="64748B"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="14"/>
+            <c:idx val="10"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -1832,7 +1922,7 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="16"/>
+            <c:idx val="15"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -1858,19 +1948,6 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="19"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="0EA5E9"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
             <c:idx val="20"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
@@ -1884,12 +1961,25 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="21"/>
+            <c:idx val="22"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="0EA5E9"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="23"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="64748B"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1915,7 +2005,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="64748B"/>
+                <a:srgbClr val="0EA5E9"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1936,7 +2026,7 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="28"/>
+            <c:idx val="31"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -1949,12 +2039,12 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="30"/>
+            <c:idx val="32"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="0EA5E9"/>
+                <a:srgbClr val="64748B"/>
               </a:solidFill>
               <a:ln>
                 <a:noFill/>
@@ -1993,6 +2083,45 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
+                <a:srgbClr val="0EA5E9"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="39"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0EA5E9"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="40"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="0EA5E9"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="42"/>
+            <c:invertIfNegative val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
                 <a:srgbClr val="64748B"/>
               </a:solidFill>
               <a:ln>
@@ -2001,7 +2130,7 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="37"/>
+            <c:idx val="43"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -2018,10 +2147,10 @@
           </c:dLbls>
           <c:val>
             <c:numRef>
-              <c:f>任务计划!$E$2:$E$39</c:f>
+              <c:f>任务计划!$E$2:$E$45</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="38"/>
+                <c:ptCount val="44"/>
                 <c:pt idx="0">
                   <c:v>2</c:v>
                 </c:pt>
@@ -2044,37 +2173,37 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>3</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>1</c:v>
@@ -2083,7 +2212,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>2</c:v>
@@ -2092,10 +2221,10 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>2</c:v>
@@ -2107,7 +2236,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2</c:v>
@@ -2116,24 +2245,42 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="37">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="38">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="39">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="40">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="41">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="42">
                   <c:v>1</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="43">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -2150,11 +2297,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="651536788"/>
-        <c:axId val="251733671"/>
+        <c:axId val="524364172"/>
+        <c:axId val="742532945"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="651536788"/>
+        <c:axId val="524364172"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2179,7 +2326,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="251733671"/>
+        <c:crossAx val="742532945"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2187,7 +2334,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="251733671"/>
+        <c:axId val="742532945"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="16"/>
@@ -2241,7 +2388,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="651536788"/>
+        <c:crossAx val="524364172"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2274,15 +2421,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>79375</xdr:colOff>
+      <xdr:colOff>603250</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>517525</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>603250</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2625,12 +2772,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:J45"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="34.625" customWidth="1"/>
-    <col min="9" max="9" width="16.625" customWidth="1"/>
-    <col min="10" max="10" width="22.625" customWidth="1"/>
+    <col min="2" max="2" width="34.6363636363636" customWidth="1"/>
+    <col min="9" max="9" width="16.6363636363636" customWidth="1"/>
+    <col min="10" max="10" width="22.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -2903,33 +3050,33 @@
         <v>3</v>
       </c>
       <c r="E9" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C10" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D10" s="2">
         <v>3</v>
@@ -2938,16 +3085,16 @@
         <v>2</v>
       </c>
       <c r="F10" s="2">
-        <v>3.35</v>
+        <v>0.75</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>46</v>
@@ -2964,295 +3111,295 @@
         <v>38</v>
       </c>
       <c r="D11" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="2">
-        <v>2.5</v>
+        <v>0.75</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2">
-        <v>5</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2</v>
-      </c>
-      <c r="F12" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2">
+        <v>3</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="2">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E15" s="2">
         <v>2</v>
       </c>
       <c r="F15" s="2">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E16" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="2">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>64</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D17" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="2">
         <v>2</v>
       </c>
       <c r="F17" s="2">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D18" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E18" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="2">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>62</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2">
         <v>1.5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D20" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
@@ -3261,94 +3408,94 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D21" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2">
         <v>2</v>
       </c>
       <c r="F21" s="2">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D22" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="2">
         <v>2.5</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D23" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2">
         <v>2</v>
@@ -3357,27 +3504,27 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D24" s="2">
         <v>8</v>
@@ -3386,13 +3533,13 @@
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>2.5</v>
+        <v>1.65</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>80</v>
@@ -3409,25 +3556,25 @@
         <v>96</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D25" s="2">
         <v>9</v>
       </c>
       <c r="E25" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>97</v>
@@ -3447,16 +3594,16 @@
         <v>9</v>
       </c>
       <c r="E26" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>95</v>
@@ -3476,167 +3623,167 @@
         <v>38</v>
       </c>
       <c r="D27" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2">
         <v>2</v>
       </c>
       <c r="F27" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J27" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D28" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" s="2">
         <v>2</v>
       </c>
       <c r="F28" s="2">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D29" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="2">
         <v>2</v>
       </c>
       <c r="F29" s="2">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D30" s="2">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2">
+        <v>3</v>
+      </c>
+      <c r="F30" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="2">
-        <v>11</v>
-      </c>
-      <c r="E30" s="2">
-        <v>2</v>
-      </c>
-      <c r="F30" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D31" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E31" s="2">
         <v>2</v>
       </c>
       <c r="F31" s="2">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D32" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E32" s="2">
         <v>2</v>
@@ -3645,222 +3792,222 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D33" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="2">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="2">
-        <v>13</v>
-      </c>
-      <c r="E34" s="2">
-        <v>1</v>
-      </c>
-      <c r="F34" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D35" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E35" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>123</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>38</v>
       </c>
       <c r="D36" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="2">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D37" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="2">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="2">
+        <v>11</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="J38" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="2">
-        <v>14</v>
-      </c>
-      <c r="E38" s="2">
-        <v>1</v>
-      </c>
-      <c r="F38" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D39" s="2">
         <v>12</v>
-      </c>
-      <c r="D39" s="2">
-        <v>15</v>
       </c>
       <c r="E39" s="2">
         <v>1</v>
@@ -3869,16 +4016,208 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="2">
+        <v>13</v>
+      </c>
+      <c r="E40" s="2">
+        <v>1</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D41" s="2">
+        <v>13</v>
+      </c>
+      <c r="E41" s="2">
+        <v>1</v>
+      </c>
+      <c r="F41" s="2">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" s="2">
+        <v>13</v>
+      </c>
+      <c r="E42" s="2">
+        <v>1</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D43" s="2">
+        <v>14</v>
+      </c>
+      <c r="E43" s="2">
+        <v>1</v>
+      </c>
+      <c r="F43" s="2">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="2">
+        <v>14</v>
+      </c>
+      <c r="E44" s="2">
+        <v>1</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="2">
+        <v>15</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>145</v>
+      <c r="I45" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
+++ b/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="166">
   <si>
     <t>任务编号</t>
   </si>
@@ -157,73 +157,79 @@
     <t>T2.1</t>
   </si>
   <si>
-    <t>T2.1 调研方案与问卷设计</t>
-  </si>
-  <si>
-    <t>调研方案、问卷与访谈提纲</t>
+    <t>T2.1 ① 复查系统规模和目标</t>
+  </si>
+  <si>
+    <t>系统规模与目标复查清单</t>
   </si>
   <si>
     <t>T2.2</t>
   </si>
   <si>
-    <t>T2.2 问卷发放与回收（≥200 份）</t>
+    <t>T2.2 ② 研究现有（正在使用）的系统</t>
+  </si>
+  <si>
+    <t>现有系统分析：问卷、竞品对比表、群内观察记录</t>
+  </si>
+  <si>
+    <t>T2.3</t>
+  </si>
+  <si>
+    <t>T2.3 ③ 导出新系统的高层逻辑模型</t>
   </si>
   <si>
     <t>W5</t>
   </si>
   <si>
-    <t>问卷原始数据</t>
-  </si>
-  <si>
-    <t>T2.3</t>
-  </si>
-  <si>
-    <t>T2.3 竞品分析与群内供需观察</t>
-  </si>
-  <si>
-    <t>竞品对比表、群内观察记录</t>
+    <t>高层数据流图、系统上下文图</t>
   </si>
   <si>
     <t>T2.4</t>
   </si>
   <si>
-    <t>T2.4 调研数据整理与统计</t>
-  </si>
-  <si>
-    <t>调研数据小结</t>
+    <t>T2.4 ④ 进一步定义问题</t>
+  </si>
+  <si>
+    <t>T2.2, T2.3</t>
+  </si>
+  <si>
+    <t>问题定义与约束清单</t>
   </si>
   <si>
     <t>T2.5</t>
   </si>
   <si>
-    <t>T2.5 技术可行性验证（云开发原型）</t>
-  </si>
-  <si>
-    <t>技术验证结论与原型截图</t>
+    <t>T2.5 ⑤ 导出和评价供选择的解法</t>
+  </si>
+  <si>
+    <t>方案对比表（三类可选方案）</t>
   </si>
   <si>
     <t>T2.6</t>
   </si>
   <si>
-    <t>T2.6 成本与效益测算</t>
-  </si>
-  <si>
-    <t>成本测算表、收益/投资比测算</t>
+    <t>T2.6 ⑥ 推荐行动方针</t>
+  </si>
+  <si>
+    <t>推荐方案与理由说明</t>
   </si>
   <si>
     <t>T2.7</t>
   </si>
   <si>
-    <t>T2.7 合规与主体资质核查</t>
-  </si>
-  <si>
-    <t>合规核查记录、资质路径结论</t>
+    <t>T2.7 ⑦ 草拟开发计划书</t>
+  </si>
+  <si>
+    <t>开发计划草案（范围/进度/资源粗估）</t>
   </si>
   <si>
     <t>T2.8</t>
   </si>
   <si>
-    <t>T2.8 可行性分析报告撰写（GB 8567）</t>
+    <t>T2.8 ⑧ 编写可行性研究报告并提交审查</t>
+  </si>
+  <si>
+    <t>T2.5, T2.7</t>
   </si>
   <si>
     <t>可行性分析报告（10/21）</t>
@@ -1552,28 +1558,28 @@
                   <c:v>T1.7 项目计划汇报 PPT 制作与宣讲</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>T2.1 调研方案与问卷设计</c:v>
+                  <c:v>T2.1 ① 复查系统规模和目标</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>T2.2 问卷发放与回收（≥200 份）</c:v>
+                  <c:v>T2.2 ② 研究现有（正在使用）的系统</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>T2.3 竞品分析与群内供需观察</c:v>
+                  <c:v>T2.3 ③ 导出新系统的高层逻辑模型</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>T2.4 调研数据整理与统计</c:v>
+                  <c:v>T2.4 ④ 进一步定义问题</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>T2.5 技术可行性验证（云开发原型）</c:v>
+                  <c:v>T2.5 ⑤ 导出和评价供选择的解法</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>T2.6 成本与效益测算</c:v>
+                  <c:v>T2.6 ⑥ 推荐行动方针</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>T2.7 合规与主体资质核查</c:v>
+                  <c:v>T2.7 ⑦ 草拟开发计划书</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>T2.8 可行性分析报告撰写（GB 8567）</c:v>
+                  <c:v>T2.8 ⑧ 编写可行性研究报告并提交审查</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>T3.1 需求获取与建模（用例/数据流）</c:v>
@@ -1702,16 +1708,16 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>4</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>3</c:v>
-                </c:pt>
                 <c:pt idx="12">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>4</c:v>
@@ -1870,19 +1876,6 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="7"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="0EA5E9"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
-          </c:dPt>
-          <c:dPt>
             <c:idx val="8"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
@@ -1896,7 +1889,7 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="9"/>
+            <c:idx val="10"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -1909,7 +1902,7 @@
             </c:spPr>
           </c:dPt>
           <c:dPt>
-            <c:idx val="10"/>
+            <c:idx val="11"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
             <c:spPr>
@@ -2176,22 +2169,22 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>2</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>1</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>1</c:v>
@@ -2297,11 +2290,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="524364172"/>
-        <c:axId val="742532945"/>
+        <c:axId val="210551408"/>
+        <c:axId val="806874079"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="524364172"/>
+        <c:axId val="210551408"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2326,7 +2319,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="742532945"/>
+        <c:crossAx val="806874079"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2334,7 +2327,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="742532945"/>
+        <c:axId val="806874079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="16"/>
@@ -2388,7 +2381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="524364172"/>
+        <c:crossAx val="210551408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3044,7 +3037,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D9" s="2">
         <v>3</v>
@@ -3053,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>27</v>
@@ -3082,39 +3075,39 @@
         <v>3</v>
       </c>
       <c r="E10" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="C11" s="2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D11" s="2">
         <v>3</v>
       </c>
       <c r="E11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="2">
         <v>0.75</v>
@@ -3123,7 +3116,7 @@
         <v>27</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>40</v>
@@ -3143,129 +3136,129 @@
         <v>38</v>
       </c>
       <c r="D12" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="2">
         <v>0.5</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="2">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="2">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="2">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>22</v>
@@ -3277,27 +3270,27 @@
         <v>1</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>38</v>
@@ -3312,24 +3305,24 @@
         <v>2.5</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>22</v>
@@ -3344,24 +3337,24 @@
         <v>2.5</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>12</v>
@@ -3376,24 +3369,24 @@
         <v>1.5</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>22</v>
@@ -3408,24 +3401,24 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>22</v>
@@ -3440,24 +3433,24 @@
         <v>2.5</v>
       </c>
       <c r="G21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="J21" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>38</v>
@@ -3472,24 +3465,24 @@
         <v>2.5</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>22</v>
@@ -3504,24 +3497,24 @@
         <v>2</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="J23" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>38</v>
@@ -3536,24 +3529,24 @@
         <v>1.65</v>
       </c>
       <c r="G24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>12</v>
@@ -3568,24 +3561,24 @@
         <v>1.5</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>22</v>
@@ -3600,24 +3593,24 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>38</v>
@@ -3632,24 +3625,24 @@
         <v>1.5</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>38</v>
@@ -3664,24 +3657,24 @@
         <v>2.5</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>38</v>
@@ -3696,24 +3689,24 @@
         <v>2</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>22</v>
@@ -3728,24 +3721,24 @@
         <v>2.5</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>22</v>
@@ -3760,24 +3753,24 @@
         <v>2.5</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>22</v>
@@ -3792,24 +3785,24 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>38</v>
@@ -3824,24 +3817,24 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>12</v>
@@ -3856,24 +3849,24 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>38</v>
@@ -3888,24 +3881,24 @@
         <v>1.5</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>38</v>
@@ -3920,24 +3913,24 @@
         <v>1.5</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>22</v>
@@ -3952,24 +3945,24 @@
         <v>1.5</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>38</v>
@@ -3984,24 +3977,24 @@
         <v>1</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>22</v>
@@ -4016,24 +4009,24 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>22</v>
@@ -4048,24 +4041,24 @@
         <v>1.5</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>38</v>
@@ -4080,24 +4073,24 @@
         <v>2</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>38</v>
@@ -4112,24 +4105,24 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>22</v>
@@ -4144,24 +4137,24 @@
         <v>2</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>12</v>
@@ -4176,24 +4169,24 @@
         <v>1.5</v>
       </c>
       <c r="G44" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="H44" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="J44" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>12</v>
@@ -4214,10 +4207,10 @@
         <v>31</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
+++ b/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
@@ -49,7 +49,7 @@
     <t>工期周数</t>
   </si>
   <si>
-    <t>工期人天</t>
+    <t>工期人时</t>
   </si>
   <si>
     <t>开始周</t>
@@ -1491,7 +1491,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1400"/>
-              <a:t>校园互助平台项目 · 任务级甘特图（W1–W16，9/16–1/6）</a:t>
+              <a:t>校园互助平台项目 · 任务级甘特图（2026/09/14–2027/01/08）</a:t>
             </a:r>
             <a:endParaRPr sz="1400"/>
           </a:p>
@@ -2290,11 +2290,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="210551408"/>
-        <c:axId val="806874079"/>
+        <c:axId val="153313404"/>
+        <c:axId val="470936283"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="210551408"/>
+        <c:axId val="153313404"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2319,7 +2319,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="806874079"/>
+        <c:crossAx val="470936283"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2327,7 +2327,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="806874079"/>
+        <c:axId val="470936283"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="16"/>
@@ -2381,7 +2381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="210551408"/>
+        <c:crossAx val="153313404"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2822,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>13</v>
@@ -2854,7 +2854,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>14</v>
@@ -2886,7 +2886,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>14</v>
@@ -2918,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>27</v>
@@ -2950,7 +2950,7 @@
         <v>15</v>
       </c>
       <c r="F6" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>14</v>
@@ -2982,7 +2982,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>27</v>
@@ -3014,7 +3014,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>23</v>
@@ -3046,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>27</v>
@@ -3078,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>27</v>
@@ -3110,7 +3110,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="2">
-        <v>0.75</v>
+        <v>6</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>27</v>
@@ -3142,7 +3142,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>27</v>
@@ -3174,7 +3174,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>48</v>
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>48</v>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="2">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>48</v>
@@ -3270,7 +3270,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="2">
-        <v>0.85</v>
+        <v>6.8</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>48</v>
@@ -3302,7 +3302,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>69</v>
@@ -3334,7 +3334,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>69</v>
@@ -3366,7 +3366,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>69</v>
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>80</v>
@@ -3430,7 +3430,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>80</v>
@@ -3462,7 +3462,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>70</v>
@@ -3494,7 +3494,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>84</v>
@@ -3526,7 +3526,7 @@
         <v>3</v>
       </c>
       <c r="F24" s="2">
-        <v>1.65</v>
+        <v>13.2</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>84</v>
@@ -3558,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>91</v>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>91</v>
@@ -3622,7 +3622,7 @@
         <v>2</v>
       </c>
       <c r="F27" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>84</v>
@@ -3654,7 +3654,7 @@
         <v>2</v>
       </c>
       <c r="F28" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>91</v>
@@ -3686,7 +3686,7 @@
         <v>2</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>91</v>
@@ -3718,7 +3718,7 @@
         <v>3</v>
       </c>
       <c r="F30" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>84</v>
@@ -3750,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="F31" s="2">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>91</v>
@@ -3782,7 +3782,7 @@
         <v>2</v>
       </c>
       <c r="F32" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>91</v>
@@ -3814,7 +3814,7 @@
         <v>2</v>
       </c>
       <c r="F33" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>95</v>
@@ -3846,7 +3846,7 @@
         <v>2</v>
       </c>
       <c r="F34" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>95</v>
@@ -3878,7 +3878,7 @@
         <v>2</v>
       </c>
       <c r="F35" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>95</v>
@@ -3910,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="F36" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>123</v>
@@ -3942,7 +3942,7 @@
         <v>2</v>
       </c>
       <c r="F37" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>123</v>
@@ -3974,7 +3974,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>123</v>
@@ -4006,7 +4006,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>134</v>
@@ -4038,7 +4038,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>148</v>
@@ -4070,7 +4070,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>148</v>
@@ -4102,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>148</v>
@@ -4134,7 +4134,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>158</v>
@@ -4166,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="2">
-        <v>1.5</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>158</v>
@@ -4198,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>

--- a/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
+++ b/design/SE2026-G22-校园互助平台-甘特图(WPS制作).xlsx
@@ -2290,11 +2290,11 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="153313404"/>
-        <c:axId val="470936283"/>
+        <c:axId val="495384939"/>
+        <c:axId val="996163904"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="153313404"/>
+        <c:axId val="495384939"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2319,7 +2319,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="470936283"/>
+        <c:crossAx val="996163904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2327,7 +2327,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="470936283"/>
+        <c:axId val="996163904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="16"/>
@@ -2381,7 +2381,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="153313404"/>
+        <c:crossAx val="495384939"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -2439,6 +2439,42 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>101600</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2" descr="logo"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="101600" y="101600"/>
+          <a:ext cx="990600" cy="990600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
